--- a/Final_Dataset.xlsx
+++ b/Final_Dataset.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U1171032\Downloads\Data Organisation\Claude\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U1171032\Downloads\Data Organisation\Claude\wii_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8117A177-E461-4D23-A201-396E4D47F04D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00855DC4-F2B1-4414-A70A-8B32561933CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="705" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{353E6ED1-C078-4E85-9FCA-27C493A7D543}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{353E6ED1-C078-4E85-9FCA-27C493A7D543}"/>
   </bookViews>
   <sheets>
     <sheet name="Carango" sheetId="1" r:id="rId1"/>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="4">
-        <v>4.2724615384615374</v>
+        <v>5.77</v>
       </c>
       <c r="E9" s="5">
         <v>2.4319989681243901</v>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="4">
-        <v>3.3722307692307689</v>
+        <v>4.3490000000000002</v>
       </c>
       <c r="E10" s="5">
         <v>1.1540291309356689</v>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="4">
-        <v>4.0641538461538467</v>
+        <v>5.2009999999999996</v>
       </c>
       <c r="E11" s="5">
         <v>2.1364493370056148</v>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="4">
-        <v>3.1093846153846152</v>
+        <v>5.0419999999999998</v>
       </c>
       <c r="E12" s="5">
         <v>3.0443763732910161</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="4">
-        <v>2.2153846153846155</v>
+        <v>2.944</v>
       </c>
       <c r="E13" s="5">
         <v>0.94091016054153442</v>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="4">
-        <v>4.023538461538462</v>
+        <v>5.4260000000000002</v>
       </c>
       <c r="E14" s="5">
         <v>2.0041427612304692</v>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="4">
-        <v>3.2696153846153844</v>
+        <v>3.738</v>
       </c>
       <c r="E15" s="5">
         <v>2.5351207256317139</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="4">
-        <v>2.8250000000000002</v>
+        <v>4.2279999999999998</v>
       </c>
       <c r="E16" s="5">
         <v>2.1883080005645752</v>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="4">
-        <v>3.6451538461538462</v>
+        <v>3.359</v>
       </c>
       <c r="E17" s="5">
         <v>2.8200254440307622</v>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="4">
-        <v>3.7899230769230767</v>
+        <v>5.4080000000000004</v>
       </c>
       <c r="E18" s="5">
         <v>2.771886825561523</v>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="4">
-        <v>4.6159230769230764</v>
+        <v>5.3310000000000004</v>
       </c>
       <c r="E19" s="5">
         <v>2.8077197074890141</v>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="4">
-        <v>3.3463846153846148</v>
+        <v>3.65</v>
       </c>
       <c r="E20" s="5">
         <v>2.234656810760498</v>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="4">
-        <v>3.0196923076923081</v>
+        <v>1.887</v>
       </c>
       <c r="E21" s="5">
         <v>0.61480289697647095</v>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="4">
-        <v>4.3390000000000004</v>
+        <v>4.8280000000000003</v>
       </c>
       <c r="E22" s="5">
         <v>2.0675003528594971</v>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="C23" s="3"/>
       <c r="D23" s="4">
-        <v>1.5996923076923077</v>
+        <v>3.5350000000000001</v>
       </c>
       <c r="E23" s="5">
         <v>0.84713149070739746</v>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="C24" s="3"/>
       <c r="D24" s="4">
-        <v>1.3066923076923078</v>
+        <v>3.6379999999999999</v>
       </c>
       <c r="E24" s="5">
         <v>2.1948318481445308</v>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="4">
-        <v>1.1193846153846154</v>
+        <v>2.032</v>
       </c>
       <c r="E25" s="5">
         <v>0.81705141067504883</v>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="C26" s="3"/>
       <c r="D26" s="4">
-        <v>3.0199230769230772</v>
+        <v>3.87</v>
       </c>
       <c r="E26" s="5">
         <v>0.56060177087783813</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C27" s="3"/>
       <c r="D27" s="4">
-        <v>2.6506923076923075</v>
+        <v>2.2839999999999998</v>
       </c>
       <c r="E27" s="5">
         <v>1.1847108602523799</v>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="4">
-        <v>2.7908461538461542</v>
+        <v>3.0419999999999998</v>
       </c>
       <c r="E28" s="5">
         <v>1.2262980937957759</v>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="C29" s="3"/>
       <c r="D29" s="4">
-        <v>4.1665384615384617</v>
+        <v>5.8819999999999997</v>
       </c>
       <c r="E29" s="5">
         <v>2.9512138366699219</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="4">
-        <v>43.486999999999995</v>
+        <v>3.0619999999999998</v>
       </c>
       <c r="E30" s="5">
         <v>2.0783565044403081</v>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="C31" s="3"/>
       <c r="D31" s="4">
-        <v>2.9789230769230768</v>
+        <v>3.5710000000000002</v>
       </c>
       <c r="E31" s="5">
         <v>1.598604679107666</v>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="C32" s="3"/>
       <c r="D32" s="6">
-        <v>3.0297692307692308</v>
+        <v>3.7010000000000001</v>
       </c>
       <c r="E32" s="5">
         <v>1.894853949546814</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="6">
-        <v>3.8306923076923081</v>
+        <v>3.3769999999999998</v>
       </c>
       <c r="E33" s="5">
         <v>1.9177103042602539</v>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="6">
-        <v>4.0219230769230769</v>
+        <v>4.5960000000000001</v>
       </c>
       <c r="E34" s="5">
         <v>1.96021568775177</v>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="6">
-        <v>3.3341538461538462</v>
+        <v>4.8559999999999999</v>
       </c>
       <c r="E35" s="5">
         <v>2.8084065914154048</v>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C36" s="3"/>
       <c r="D36" s="6">
-        <v>3.8917692307692304</v>
+        <v>4.6289999999999996</v>
       </c>
       <c r="E36" s="5">
         <v>1.077924966812134</v>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="C37" s="3"/>
       <c r="D37" s="6">
-        <v>1.7849230769230771</v>
+        <v>3.7709999999999999</v>
       </c>
       <c r="E37" s="5">
         <v>0.863700270652771</v>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="C38" s="3"/>
       <c r="D38" s="6">
-        <v>3.1215384615384614</v>
+        <v>3.65</v>
       </c>
       <c r="E38" s="5">
         <v>0.7570154070854187</v>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="C39" s="3"/>
       <c r="D39" s="6">
-        <v>4.3002307692307689</v>
+        <v>3.59</v>
       </c>
       <c r="E39" s="5">
         <v>2.3723404407501221</v>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="6">
-        <v>2.8718461538461542</v>
+        <v>5.5419999999999998</v>
       </c>
       <c r="E40" s="5">
         <v>2.6088082790374751</v>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="C41" s="3"/>
       <c r="D41" s="6">
-        <v>4.3478461538461541</v>
+        <v>5.2309999999999999</v>
       </c>
       <c r="E41" s="5">
         <v>2.7453770637512211</v>
